--- a/artfynd/A 60839-2021 artfynd.xlsx
+++ b/artfynd/A 60839-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 60839-2021 artfynd.xlsx
+++ b/artfynd/A 60839-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1055,6 +1055,127 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124198769</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58196</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>rastande</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hitorpsbadet, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>502449</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6596565</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Renate Schwencke</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Renate Schwencke</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60839-2021 artfynd.xlsx
+++ b/artfynd/A 60839-2021 artfynd.xlsx
@@ -1060,7 +1060,7 @@
         <v>124198769</v>
       </c>
       <c r="B5" t="n">
-        <v>58605</v>
+        <v>58607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60839-2021 artfynd.xlsx
+++ b/artfynd/A 60839-2021 artfynd.xlsx
@@ -1060,7 +1060,7 @@
         <v>124198769</v>
       </c>
       <c r="B5" t="n">
-        <v>58607</v>
+        <v>58608</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60839-2021 artfynd.xlsx
+++ b/artfynd/A 60839-2021 artfynd.xlsx
@@ -1060,7 +1060,7 @@
         <v>124198769</v>
       </c>
       <c r="B5" t="n">
-        <v>58613</v>
+        <v>58619</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60839-2021 artfynd.xlsx
+++ b/artfynd/A 60839-2021 artfynd.xlsx
@@ -1060,7 +1060,7 @@
         <v>124198769</v>
       </c>
       <c r="B5" t="n">
-        <v>58619</v>
+        <v>58620</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60839-2021 artfynd.xlsx
+++ b/artfynd/A 60839-2021 artfynd.xlsx
@@ -1060,7 +1060,7 @@
         <v>124198769</v>
       </c>
       <c r="B5" t="n">
-        <v>58620</v>
+        <v>58623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60839-2021 artfynd.xlsx
+++ b/artfynd/A 60839-2021 artfynd.xlsx
@@ -1060,7 +1060,7 @@
         <v>124198769</v>
       </c>
       <c r="B5" t="n">
-        <v>58623</v>
+        <v>58625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 60839-2021 artfynd.xlsx
+++ b/artfynd/A 60839-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66700341</v>
+        <v>60575059</v>
       </c>
       <c r="B2" t="n">
-        <v>96370</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219875</v>
+        <v>102961</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönvit nattviol</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera chlorantha</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Custer) Rchb.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,27 +708,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kristianlund, hitorp, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502541.2917720958</v>
+        <v>502541</v>
       </c>
       <c r="R2" t="n">
-        <v>6596486.784014151</v>
+        <v>6596487</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -760,22 +751,27 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
+          <t>2016-07-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
+          <t>2016-07-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Nere vid vattnet.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,44 +791,39 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Billy Lindblom, Fredrika Nybäck-Ragnarson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66700352</v>
+        <v>60953930</v>
       </c>
       <c r="B3" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221343</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,27 +831,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>revir, ej häckning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kristianlund, hitorp, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502541.2917720958</v>
+        <v>502541</v>
       </c>
       <c r="R3" t="n">
-        <v>6596486.784014151</v>
+        <v>6596487</v>
       </c>
       <c r="S3" t="n">
         <v>75</v>
@@ -887,22 +874,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2017-07-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-08-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,15 +906,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60575059</v>
+        <v>124198769</v>
       </c>
       <c r="B4" t="n">
-        <v>55903</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>58676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -945,16 +917,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102961</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -967,26 +939,24 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>rastande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kristianlund, hitorp, Nora sn, Vstm</t>
+          <t>Hitorpsbadet, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502541.2917720958</v>
+        <v>502449</v>
       </c>
       <c r="R4" t="n">
-        <v>6596486.784014151</v>
+        <v>6596565</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1010,27 +980,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-07-15</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-07-15</t>
+          <t>2025-04-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Nere vid vattnet.</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1045,44 +1010,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Billy Lindblom</t>
+          <t>Renate Schwencke</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Billy Lindblom, Fredrika Nybäck-Ragnarson</t>
+          <t>Renate Schwencke</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124198769</v>
+        <v>66700341</v>
       </c>
       <c r="B5" t="n">
-        <v>58625</v>
+        <v>99156</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103055</v>
+        <v>219875</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönvit nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Platanthera chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Custer) Rchb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1090,24 +1055,30 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>rastande</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hitorpsbadet, Vstm</t>
+          <t>Kristianlund, hitorp, Nora sn, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502449</v>
+        <v>502541</v>
       </c>
       <c r="R5" t="n">
-        <v>6596565</v>
+        <v>6596487</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1131,22 +1102,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2017-07-14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-04-18</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2017-07-14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1161,15 +1122,127 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Renate Schwencke</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Renate Schwencke</t>
+          <t>Billy Lindblom</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>66700352</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Kristianlund, hitorp, Nora sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>502541</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6596487</v>
+      </c>
+      <c r="S6" t="n">
+        <v>75</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-07-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-07-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Billy Lindblom</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 60839-2021 artfynd.xlsx
+++ b/artfynd/A 60839-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60575059</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60953930</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124198769</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66700341</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,8 +1268,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66700352</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>